--- a/DXLibProject_Start/Data/CSV/CameraParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CameraParam.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDAEB11-B0CA-418B-B5F9-4149759CA9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F2BE7D-C47F-45C6-BB22-BE50475AF7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{03E13551-9E72-4A66-B263-B26794078B74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03E13551-9E72-4A66-B263-B26794078B74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -525,7 +525,7 @@
         <v>400</v>
       </c>
       <c r="H2">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -534,5 +534,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DXLibProject_Start/Data/CSV/CameraParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CameraParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F2BE7D-C47F-45C6-BB22-BE50475AF7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D82DFB-7A7A-4893-8DA2-7E749CE75B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03E13551-9E72-4A66-B263-B26794078B74}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{03E13551-9E72-4A66-B263-B26794078B74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0.0,100.0,0.0</t>
+    <t>0.0,150.0,0.0</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -510,16 +510,16 @@
         <v>600</v>
       </c>
       <c r="C2">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="D2">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="E2">
         <v>-45</v>
       </c>
       <c r="F2">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="G2">
         <v>400</v>

--- a/DXLibProject_Start/Data/CSV/CameraParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CameraParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D82DFB-7A7A-4893-8DA2-7E749CE75B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D038E9C-61AD-485F-BAE8-20D0EAA49DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{03E13551-9E72-4A66-B263-B26794078B74}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{03E13551-9E72-4A66-B263-B26794078B74}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -516,7 +516,7 @@
         <v>750</v>
       </c>
       <c r="E2">
-        <v>-45</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>85</v>
